--- a/working/CrizerPFAS/Hep13-Hep14-to-JFW_PFAS.xlsx
+++ b/working/CrizerPFAS/Hep13-Hep14-to-JFW_PFAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwambaug\git\invitrotkstats\working\CrizerPFAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2D4C0D-0475-4FED-B4A0-991658C881BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330F6B4C-CB27-4BBC-9713-291017FB1BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{3AB15C33-727A-4B46-8F41-3E88A8B9857E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{3AB15C33-727A-4B46-8F41-3E88A8B9857E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hep13 Raw Data for JFW" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6457" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6461" uniqueCount="555">
   <si>
     <t>Hep14 Run</t>
   </si>
@@ -1700,6 +1700,9 @@
   <si>
     <t>bd</t>
   </si>
+  <si>
+    <t>NoColName</t>
+  </si>
 </sst>
 </file>
 
@@ -24174,6 +24177,9 @@
       <c r="N20" t="s">
         <v>39</v>
       </c>
+      <c r="O20" t="s">
+        <v>554</v>
+      </c>
       <c r="P20" s="1" t="s">
         <v>40</v>
       </c>
@@ -31904,6 +31910,9 @@
       <c r="N216" t="s">
         <v>39</v>
       </c>
+      <c r="O216" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217">
@@ -39480,6 +39489,9 @@
       <c r="N412" t="s">
         <v>39</v>
       </c>
+      <c r="O412" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="413" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A413">
@@ -47973,6 +47985,9 @@
       </c>
       <c r="N608" t="s">
         <v>39</v>
+      </c>
+      <c r="O608" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="609" spans="1:15" x14ac:dyDescent="0.35">
